--- a/erp-server/erp-server-file/src/main/resources/excel/wms/soDeliveryNoticeChangeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/wms/soDeliveryNoticeChangeExport.xlsx
@@ -107,7 +107,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.salesQty}</t>
+    <t>{.saleQty}</t>
   </si>
   <si>
     <t>{.allNoticeQty}</t>
